--- a/Project Outputs for UZ_D_Inverter/Rev02/BOM/BOM_UZ_D_Inverter_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_D_Inverter/Rev02/BOM/BOM_UZ_D_Inverter_[No Variations]_Rev02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hufnagel\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UltraZohm\uz_d_inverter\Project Outputs for UZ_D_Inverter\Rev02\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E24BFD6-65B7-41F1-9896-ADAECB096206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB8E538-FF04-46E5-A165-5FE592D0622D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="24930" windowWidth="23040" windowHeight="12270" xr2:uid="{4EBBC224-ACF2-4F2F-8DE9-61D1CCB195BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F449D50D-4A7D-459B-9B33-2B20BBEEB103}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_D_Inverter_ No Variation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="283">
   <si>
     <t>Designator</t>
   </si>
@@ -71,7 +71,7 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Manufacturer_Part_Number</t>
+    <t>Manufacturer Part Number</t>
   </si>
   <si>
     <t>C1, C9A, C9B, C9C, C105</t>
@@ -98,21 +98,27 @@
     <t>1 µF</t>
   </si>
   <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>Capacitor 1206, 35 VDC, 10 µF, X5R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">581-1206DD106MAT2A </t>
-  </si>
-  <si>
-    <t>C_1206</t>
+    <t xml:space="preserve">C0603C105K3RAC7411 </t>
+  </si>
+  <si>
+    <t>C2, C81, C82, C83, C85, C86, C87, C88, C89, C90, C91</t>
+  </si>
+  <si>
+    <t>Capacitor 1210, 100 VDC, 10µF, X7S</t>
+  </si>
+  <si>
+    <t>81-GRM32EC72A106KE05</t>
+  </si>
+  <si>
+    <t>C_1210_N</t>
   </si>
   <si>
     <t>10 µF</t>
   </si>
   <si>
+    <t>GRM32EC72A106KE05L</t>
+  </si>
+  <si>
     <t>C3, C4, C17A, C17B, C17C, C19A, C19B, C19C, C20A, C20B, C20C, C22A, C22B, C22C, C23A, C23B, C23C, C24A, C24B, C24C, C57, C58, C59, C60, C66A, C66B, C66C, C67A, C67B, C67C, C68A, C68B, C68C, C69A, C69B, C69C, C72A, C72B, C72C, C73A, C73B, C73C, C80, C80A, C80B, C80C, C81A, C81B, C81C, C82A, C82B, C82C, C83A, C83B, C83C, C84, C99</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t>0.1 µF</t>
   </si>
   <si>
+    <t>C1608X7S2A104K080AB</t>
+  </si>
+  <si>
     <t>C10A, C10B, C10C, C18A, C18B, C18C, C21A, C21B, C21C, C25A, C25B, C25C, C26A, C26B, C26C, C52</t>
   </si>
   <si>
@@ -137,6 +146,9 @@
     <t>10 nF</t>
   </si>
   <si>
+    <t>C0603X103K3GECTU</t>
+  </si>
+  <si>
     <t>C11A, C11B, C11C, C12A, C12B, C12C, C15A, C15B, C15C, C16A, C16B, C16C, C50, C51, C55, C56</t>
   </si>
   <si>
@@ -155,6 +167,9 @@
     <t>56 pF</t>
   </si>
   <si>
+    <t>CL10C560JB8NNNC</t>
+  </si>
+  <si>
     <t>C13A, C13B, C13C, C53</t>
   </si>
   <si>
@@ -170,6 +185,9 @@
     <t>4.7 nF</t>
   </si>
   <si>
+    <t>C0805C472F1GECAUTO7210</t>
+  </si>
+  <si>
     <t>C14A, C14B, C14C, C54</t>
   </si>
   <si>
@@ -182,6 +200,9 @@
     <t>3.3 nF</t>
   </si>
   <si>
+    <t>C0805C332F1GACTU</t>
+  </si>
+  <si>
     <t>C40, C41, C42, C43, C44, C45, C46, C47, C48, C49</t>
   </si>
   <si>
@@ -197,6 +218,9 @@
     <t>47µF</t>
   </si>
   <si>
+    <t>EEV-FK2A470V</t>
+  </si>
+  <si>
     <t>C60A, C60B, C60C, C61A, C61B, C61C, C62A, C62B, C62C, C63A, C63B, C63C</t>
   </si>
   <si>
@@ -209,6 +233,9 @@
     <t>4.7 µF</t>
   </si>
   <si>
+    <t xml:space="preserve">C2012X7R1H475K125AC </t>
+  </si>
+  <si>
     <t>C64A, C64B, C64C, C65A, C65B, C65C</t>
   </si>
   <si>
@@ -221,6 +248,9 @@
     <t>2.2 uF</t>
   </si>
   <si>
+    <t>C1608X5R1E225K080AB</t>
+  </si>
+  <si>
     <t>D1</t>
   </si>
   <si>
@@ -242,6 +272,9 @@
     <t>Farnell</t>
   </si>
   <si>
+    <t xml:space="preserve">150060BS84000 </t>
+  </si>
+  <si>
     <t>D2</t>
   </si>
   <si>
@@ -254,6 +287,9 @@
     <t xml:space="preserve">3408612 </t>
   </si>
   <si>
+    <t xml:space="preserve">150060GS84000 </t>
+  </si>
+  <si>
     <t>D3</t>
   </si>
   <si>
@@ -266,19 +302,25 @@
     <t xml:space="preserve">3408608 </t>
   </si>
   <si>
+    <t>150060RS86000</t>
+  </si>
+  <si>
     <t>F1, F2, F3</t>
   </si>
   <si>
     <t>POLYSWITCH RESETTABLE DEVICES</t>
   </si>
   <si>
-    <t>530-0ZCG0150BF2C</t>
-  </si>
-  <si>
-    <t>1812_PTC_Polyfuse_Littelfuse</t>
-  </si>
-  <si>
-    <t>PTC, 1.1 A, 24V</t>
+    <t>650-MINIASMDC110F/24</t>
+  </si>
+  <si>
+    <t>MINIASMDC260F162</t>
+  </si>
+  <si>
+    <t>PPTC, 1.1 A, 24V</t>
+  </si>
+  <si>
+    <t>MINIASMDC110F/24-2</t>
   </si>
   <si>
     <t>J1, J2</t>
@@ -317,6 +359,9 @@
     <t>PCB mount 4mm jack, Red FCR7350R, 1000V, 24A</t>
   </si>
   <si>
+    <t>FCR7350R</t>
+  </si>
+  <si>
     <t>J4</t>
   </si>
   <si>
@@ -335,6 +380,9 @@
     <t>PCB mount 4mm jack, Blue FCR7350L, 1000V, 24A</t>
   </si>
   <si>
+    <t>FCR7350L</t>
+  </si>
+  <si>
     <t>J5, J6, J7</t>
   </si>
   <si>
@@ -353,6 +401,27 @@
     <t>PCB mount 4mm jack, Black	FCR7350B, 1000V, 24A</t>
   </si>
   <si>
+    <t>FCR7350B</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>8 Pin</t>
+  </si>
+  <si>
+    <t>571-103741-8</t>
+  </si>
+  <si>
+    <t>Pin Header</t>
+  </si>
+  <si>
+    <t>HDR1X8</t>
+  </si>
+  <si>
+    <t>103741-8</t>
+  </si>
+  <si>
     <t>L1A, L1B, L1C, L2A, L2B, L2C, L3A, L3B, L3C, L4A, L4B, L4C, L5A, L5B, L5C, L6, L7, L8, L9A, L9B, L9C, L10A, L10B, L10C, L11, L12</t>
   </si>
   <si>
@@ -371,6 +440,9 @@
     <t>6.8uH</t>
   </si>
   <si>
+    <t>LQM18DN6R8M70L</t>
+  </si>
+  <si>
     <t>PS1A, PS1B, PS1C, PS2A, PS2B, PS2C</t>
   </si>
   <si>
@@ -389,6 +461,9 @@
     <t>1 W</t>
   </si>
   <si>
+    <t>PDSE1-S24-S12-M-TR</t>
+  </si>
+  <si>
     <t>Q1A, Q1B, Q1C, Q2A, Q2B, Q2C</t>
   </si>
   <si>
@@ -425,6 +500,9 @@
     <t>0R</t>
   </si>
   <si>
+    <t>RC0603JR-070RL</t>
+  </si>
+  <si>
     <t>R4</t>
   </si>
   <si>
@@ -434,6 +512,9 @@
     <t>1k</t>
   </si>
   <si>
+    <t>RK73B1JTTDD102J</t>
+  </si>
+  <si>
     <t>R6</t>
   </si>
   <si>
@@ -443,6 +524,9 @@
     <t>2k</t>
   </si>
   <si>
+    <t>RK73B1JTTDD202J</t>
+  </si>
+  <si>
     <t>R7</t>
   </si>
   <si>
@@ -452,6 +536,9 @@
     <t>820R</t>
   </si>
   <si>
+    <t>RK73B1JTTDD821J</t>
+  </si>
+  <si>
     <t>R8</t>
   </si>
   <si>
@@ -461,6 +548,9 @@
     <t>180R</t>
   </si>
   <si>
+    <t>RK73B1JTTDD181J</t>
+  </si>
+  <si>
     <t>R10A, R10B, R10C, R50</t>
   </si>
   <si>
@@ -476,7 +566,10 @@
     <t>2mR</t>
   </si>
   <si>
-    <t>R12A, R12B, R12C, R13A, R13B, R13C, R53, R54, R124A, R124B, R124C, R127</t>
+    <t>PU3921FKMP50R002L</t>
+  </si>
+  <si>
+    <t>R12A, R12B, R12C, R13A, R13B, R13C, R53, R54, R86A, R86B, R86C, R127</t>
   </si>
   <si>
     <t>SMD resistor 0.1%</t>
@@ -485,12 +578,18 @@
     <t>66-PCFW0603LF031001B</t>
   </si>
   <si>
+    <t xml:space="preserve">PCF-W0603LF-03-1001-B-P-LT </t>
+  </si>
+  <si>
     <t>R14A, R14B, R14C, R15A, R15B, R15C, R55, R56, R95, R97A, R97B, R97C</t>
   </si>
   <si>
     <t>667-ERJ-PB3B2001V</t>
   </si>
   <si>
+    <t>ERJ-PB3B2001V</t>
+  </si>
+  <si>
     <t>R19A, R19B, R19C, R20A, R20B, R20C, R25A, R25B, R25C, R26A, R26B, R26C, R57, R58, R67, R68</t>
   </si>
   <si>
@@ -503,6 +602,9 @@
     <t>49R9</t>
   </si>
   <si>
+    <t>RK73H1JTTD49R9F</t>
+  </si>
+  <si>
     <t>R21A, R21B, R21C, R23A, R23B, R23C, R28A, R28B, R28C, R61, R62, R72, R74, R130A, R130B, R130C</t>
   </si>
   <si>
@@ -515,6 +617,9 @@
     <t>10k</t>
   </si>
   <si>
+    <t>RQ73C1J10KBTD</t>
+  </si>
+  <si>
     <t>R22A, R22B, R22C, R24A, R24B, R24C, R27A, R27B, R27C, R60, R63, R73, R75, R129A, R129B, R129C</t>
   </si>
   <si>
@@ -524,12 +629,18 @@
     <t>110k</t>
   </si>
   <si>
+    <t>RQ73C1J110KBTD</t>
+  </si>
+  <si>
     <t>R29A, R29B, R29C, R39A, R39B, R39C, R43A, R43B, R43C, R44A, R44B, R44C, R45A, R45B, R45C, R46A, R46B, R46C</t>
   </si>
   <si>
     <t>660-RK73B1JTTD103J</t>
   </si>
   <si>
+    <t>RK73B1JTTD103J</t>
+  </si>
+  <si>
     <t>R30A, R30B, R30C, R38A, R38B, R38C</t>
   </si>
   <si>
@@ -539,6 +650,9 @@
     <t>20k</t>
   </si>
   <si>
+    <t>RK73B1JTTD203J</t>
+  </si>
+  <si>
     <t>R31A, R31B, R31C, R37A, R37B, R37C</t>
   </si>
   <si>
@@ -551,6 +665,9 @@
     <t>105k</t>
   </si>
   <si>
+    <t>CR0603-FX-1053ELF</t>
+  </si>
+  <si>
     <t>R32A, R32B, R32C, R36A, R36B, R36C</t>
   </si>
   <si>
@@ -560,6 +677,9 @@
     <t>280k</t>
   </si>
   <si>
+    <t>CR0603-FX-2803ELF</t>
+  </si>
+  <si>
     <t>R33A, R33B, R33C, R40A, R40B, R40C</t>
   </si>
   <si>
@@ -572,6 +692,9 @@
     <t>287k</t>
   </si>
   <si>
+    <t xml:space="preserve">ERJ-6ENF2873V </t>
+  </si>
+  <si>
     <t>R34A, R34B, R34C, R42A, R42B, R42C</t>
   </si>
   <si>
@@ -581,6 +704,9 @@
     <t>976k</t>
   </si>
   <si>
+    <t>CR0603-FX-9763ELF</t>
+  </si>
+  <si>
     <t>R35A, R35B, R35C, R41A, R41B, R41C</t>
   </si>
   <si>
@@ -590,13 +716,19 @@
     <t>182k</t>
   </si>
   <si>
-    <t>R94, R96, R98A, R98B, R98C, R125A, R125B, R125C</t>
-  </si>
-  <si>
-    <t>603-RT0603BRD073K88L</t>
-  </si>
-  <si>
-    <t>3k88</t>
+    <t>CR0603-FX-1823ELF</t>
+  </si>
+  <si>
+    <t>R87A, R87B, R87C, R89A, R89B, R89C, R94, R96</t>
+  </si>
+  <si>
+    <t>603-RT0603FRE073K9L</t>
+  </si>
+  <si>
+    <t>3k9</t>
+  </si>
+  <si>
+    <t>RT0603FRE073K9L</t>
   </si>
   <si>
     <t>RG1A, RG1B, RG1C, RG2A, RG2B, RG2C, RG3A, RG3B, RG3C, RG4A, RG4B, RG4C</t>
@@ -644,6 +776,9 @@
     <t>2.5 V</t>
   </si>
   <si>
+    <t>REF4132B25DBVRQ1</t>
+  </si>
+  <si>
     <t>U2A, U2B, U2C, U11</t>
   </si>
   <si>
@@ -674,6 +809,9 @@
     <t>SOT127P600X175-8N</t>
   </si>
   <si>
+    <t>ADA4940-1ARZ-R7</t>
+  </si>
+  <si>
     <t>U5A, U5B, U5C, U9A, U9B, U9C</t>
   </si>
   <si>
@@ -689,6 +827,9 @@
     <t>SON50P250X250X80-9N</t>
   </si>
   <si>
+    <t>LM57CISD-10/NOPB</t>
+  </si>
+  <si>
     <t>U6A, U6B, U6C, U8A, U8B, U8C</t>
   </si>
   <si>
@@ -701,6 +842,9 @@
     <t>SOT95P280X100-6N</t>
   </si>
   <si>
+    <t>LTC6992HS6-4#WTRMPBF</t>
+  </si>
+  <si>
     <t>U7A, U7B, U7C</t>
   </si>
   <si>
@@ -725,6 +869,9 @@
     <t>SOT95P280X145-6N</t>
   </si>
   <si>
+    <t xml:space="preserve">SN74LVC2G14DBVR </t>
+  </si>
+  <si>
     <t>X2A, X2B, X2C, X3A, X3B, X3C</t>
   </si>
   <si>
@@ -735,13 +882,19 @@
   </si>
   <si>
     <t>1_Pin_Header</t>
+  </si>
+  <si>
+    <t>4-103327-3</t>
+  </si>
+  <si>
+    <t>Grün wird beigestellt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,8 +902,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -761,6 +929,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -788,17 +961,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Gut" xfId="1" builtinId="26"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1110,13 +1289,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC1811A-7A0E-4C49-BB0A-A86B77EB93FD}">
-  <dimension ref="A1:K51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454B496F-2965-45F7-A8B5-516A04CC2AAD}">
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+    <col min="1" max="1" width="55.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="3" max="3" width="84.88671875" customWidth="1"/>
     <col min="4" max="4" width="9.21875" customWidth="1"/>
     <col min="5" max="11" width="16.33203125" customWidth="1"/>
   </cols>
@@ -1187,46 +1366,54 @@
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -1247,19 +1434,21 @@
         <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -1280,22 +1469,24 @@
         <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -1310,22 +1501,24 @@
         <v>17</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -1334,7 +1527,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G7" s="1">
         <v>4</v>
@@ -1346,19 +1539,21 @@
         <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -1367,7 +1562,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1">
         <v>4</v>
@@ -1379,52 +1574,56 @@
         <v>14</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="A9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="6">
         <v>10</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="1"/>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1433,7 +1632,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G10" s="1">
         <v>12</v>
@@ -1445,22 +1644,24 @@
         <v>14</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -1475,124 +1676,132 @@
         <v>17</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="A12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="6">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="H12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="5" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="6">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="5" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="A14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="F14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="6">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="H14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
@@ -1604,319 +1813,337 @@
         <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="A16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="6">
         <v>2</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="1"/>
+      <c r="H16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="A17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="6">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K17" s="1"/>
+      <c r="H17" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="A18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="6">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K18" s="1"/>
+      <c r="H18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="A19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="6">
         <v>3</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K19" s="1"/>
+      <c r="H19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>107</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="G20" s="1">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="G21" s="1">
+        <v>26</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="6">
         <v>6</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="H22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="6">
         <v>6</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="1">
-        <v>5</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K23" s="1"/>
+      <c r="H23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="E24" s="2" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="J24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K24" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -1926,26 +2153,28 @@
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K25" s="1"/>
+        <v>156</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -1955,26 +2184,28 @@
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K26" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -1984,94 +2215,96 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K27" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G29" s="6">
         <v>4</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="1">
-        <v>12</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K29" s="1"/>
+      <c r="H29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G30" s="1">
         <v>12</v>
@@ -2080,64 +2313,68 @@
         <v>17</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K30" s="1"/>
+        <v>156</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G31" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K31" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G32" s="1">
         <v>16</v>
@@ -2146,22 +2383,24 @@
         <v>17</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K32" s="1"/>
+        <v>186</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -2170,7 +2409,7 @@
         <v>15</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G33" s="1">
         <v>16</v>
@@ -2182,19 +2421,21 @@
         <v>14</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K33" s="1"/>
+        <v>191</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -2203,10 +2444,10 @@
         <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G34" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>17</v>
@@ -2215,57 +2456,63 @@
         <v>14</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K34" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D35" s="1"/>
+        <v>198</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E35" s="2" t="s">
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G35" s="1">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K35" s="1"/>
+        <v>191</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="D36" s="1"/>
       <c r="E36" s="2" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G36" s="1">
         <v>6</v>
@@ -2273,23 +2520,23 @@
       <c r="H36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="I36" s="1"/>
       <c r="J36" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K36" s="1"/>
+        <v>202</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
@@ -2298,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G37" s="1">
         <v>6</v>
@@ -2310,19 +2557,21 @@
         <v>14</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="K37" s="1"/>
+        <v>207</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -2331,7 +2580,7 @@
         <v>15</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="G38" s="1">
         <v>6</v>
@@ -2343,19 +2592,21 @@
         <v>14</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K38" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -2364,7 +2615,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="G39" s="1">
         <v>6</v>
@@ -2376,19 +2627,21 @@
         <v>14</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K39" s="1"/>
+        <v>216</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>14</v>
@@ -2397,7 +2650,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G40" s="1">
         <v>6</v>
@@ -2409,19 +2662,21 @@
         <v>14</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K40" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -2430,10 +2685,10 @@
         <v>15</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G41" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>17</v>
@@ -2442,19 +2697,21 @@
         <v>14</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>14</v>
@@ -2463,314 +2720,372 @@
         <v>15</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="G42" s="1">
+        <v>8</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G43" s="6">
         <v>12</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="H43" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="F44" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G44">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G44" s="1">
+      <c r="H44" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G45" s="6">
         <v>1</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G45" s="1">
+      <c r="H45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G46" s="6">
         <v>4</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G46" s="1">
+      <c r="H46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="G47" s="6">
         <v>8</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G47" s="1">
+      <c r="H47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G48" s="6">
         <v>6</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G48" s="1">
+      <c r="H48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" s="6">
         <v>6</v>
       </c>
-      <c r="H48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G49" s="1">
+      <c r="H49" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G50" s="6">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G50" s="1">
+      <c r="H50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G51" s="6">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G51" s="1">
+      <c r="H51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G52" s="1">
         <v>6</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" s="1"/>
+      <c r="H52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
